--- a/docs/all/01_TablasDescriptivas/idx3_climatico_summary_labels.xlsx
+++ b/docs/all/01_TablasDescriptivas/idx3_climatico_summary_labels.xlsx
@@ -409,7 +409,7 @@
         <v>-0.199774968</v>
       </c>
       <c r="E2">
-        <v>0.03624382213963218</v>
+        <v>0.03624382213963216</v>
       </c>
       <c r="F2">
         <v>-0.324996</v>
@@ -463,7 +463,7 @@
         <v>-0.09304</v>
       </c>
       <c r="E4">
-        <v>0.07304057643838534</v>
+        <v>0.07304057643838535</v>
       </c>
       <c r="F4">
         <v>-0.36</v>
